--- a/odezda.xlsx
+++ b/odezda.xlsx
@@ -349,7 +349,7 @@
     <t xml:space="preserve">mp802751</t>
   </si>
   <si>
-    <t xml:space="preserve">test value</t>
+    <t xml:space="preserve">testicvalue1</t>
   </si>
   <si>
     <t xml:space="preserve">Одежда</t>
@@ -367,7 +367,7 @@
     <t xml:space="preserve">Свитеррр2222</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;![CDATA[ &lt;p class="p1" style="margin:0px;font-size:13px;line-height:normal;font-family:'Helvetica Neue';"&gt;&lt;strong&gt;Майка на широких бретелях TP004&lt;/strong&gt;&lt;/p&gt; &lt;p class="p1" style="margin:0px;font-size:13px;line-height:normal;font-family:'Helvetica Neue';"&gt;Базова річ, яка виглядає дорого. Майка з широкими бретелями та акуратною посадкою, що красиво підкреслює лінію плечей і тримає форму. Вона не просвічує, щільно, але комфортно сідає по фігурі й легко комбінується з будь-яким низом.&lt;/p&gt; &lt;p class="p1" style="margin:0px;font-size:13px;line-height:normal;font-family:'Helvetica Neue';"&gt;Ідеальна як самостійний елемент у теплий сезон або як база під жакет, сорочку чи кардиган. Мінімалізм, який працює завжди.&lt;/p&gt; &lt;p class="p1" style="margin:0px;font-size:13px;line-height:normal;font-family:'Helvetica Neue';"&gt;&lt;strong&gt;Матеріал та догляд:&lt;/strong&gt; 75% віскоза ,15% нейлон, 10% еластан&lt;/p&gt; &lt;p class="p1" style="margin:0px;font-size:13px;line-height:normal;font-family:'Helvetica Neue';"&gt;• Машинне прання max t 40°C.&lt;span class="Apple-converted-space"&gt; &lt;/span&gt;&lt;/p&gt; &lt;p class="p1" style="margin:0px;font-size:13px;line-height:normal;font-family:'Helvetica Neue';"&gt;• Помірний режим сушки&lt;/p&gt; &lt;p class="p1" style="margin:0px;font-size:13px;line-height:normal;font-family:'Helvetica Neue';"&gt;• Не відбілювати&lt;/p&gt; &lt;p class="p1" style="margin:0px;font-size:13px;line-height:normal;font-family:'Helvetica Neue';"&gt;• Прасування при t до 200°C&lt;/p&gt; ]]&gt;</t>
+    <t xml:space="preserve">dcasdasd12d12 d12 d12d 12d 12d 12d 12 d12d 12 </t>
   </si>
   <si>
     <t xml:space="preserve">Кофты и свитера</t>
@@ -1230,7 +1230,7 @@
       <c r="M3" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="N3" s="4" t="s">
         <v>115</v>
       </c>
       <c r="P3" s="6" t="n">

--- a/odezda.xlsx
+++ b/odezda.xlsx
@@ -349,7 +349,7 @@
     <t xml:space="preserve">mp802751</t>
   </si>
   <si>
-    <t xml:space="preserve">testicvalue1</t>
+    <t xml:space="preserve">Testicva d dlue1</t>
   </si>
   <si>
     <t xml:space="preserve">Одежда</t>
@@ -413,7 +413,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -449,12 +449,6 @@
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
       <sz val="16"/>
@@ -532,7 +526,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -557,15 +551,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1227,13 +1217,13 @@
       <c r="L3" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="M3" s="4" t="s">
         <v>115</v>
       </c>
       <c r="N3" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="P3" s="6" t="n">
+      <c r="P3" s="5" t="n">
         <v>350</v>
       </c>
       <c r="R3" s="1" t="s">
@@ -1248,7 +1238,7 @@
       <c r="U3" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="V3" s="7" t="s">
+      <c r="V3" s="6" t="s">
         <v>119</v>
       </c>
       <c r="W3" s="1" t="s">
@@ -1257,7 +1247,7 @@
       <c r="X3" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="Y3" s="8" t="s">
+      <c r="Y3" s="7" t="s">
         <v>122</v>
       </c>
       <c r="AB3" s="1" t="s">
